--- a/omnix/style/excel/用户导入模板.xlsx
+++ b/omnix/style/excel/用户导入模板.xlsx
@@ -19,14 +19,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>用户名</t>
   </si>
   <si>
-    <t>密码</t>
-  </si>
-  <si>
     <t>姓名</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
   </si>
   <si>
     <t>13700137000</t>
-  </si>
-  <si>
-    <t>多角色</t>
   </si>
   <si>
     <t>角色</t>
@@ -101,15 +95,14 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>填写说明：橙色底色为必填项；多个角色列请手动填写并用、分隔；邮箱、备注选填。</t>
+    <t>填写说明：
+1、橙色底色为必填项；
+2、密码默认为Aa123456；
+3、邮箱、备注选填。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>管理员、成员</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Aa123456$</t>
+    <t>管理员</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -220,10 +213,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -233,6 +222,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -535,31 +528,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="17.875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="17.875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-    </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,21 +568,18 @@
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
@@ -598,25 +587,22 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
@@ -624,23 +610,20 @@
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
@@ -648,200 +631,178 @@
       <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E5" s="3"/>
+      <c r="F5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E6" s="5"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E7" s="5"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E8" s="5"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E9" s="5"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E10" s="5"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E11" s="5"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E12" s="5"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E13" s="5"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E14" s="5"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E15" s="5"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E16" s="5"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E17" s="5"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E18" s="5"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E19" s="5"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E20" s="5"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E21" s="5"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" promptTitle="角色填写" prompt="请选择“是”或“否”" sqref="G6:G22">
+    <dataValidation type="list" allowBlank="1" promptTitle="角色填写" prompt="请选择“是”或“否”" sqref="F6:F22">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" promptTitle="角色填写" prompt="请选择“是”或“否”" sqref="G3:G5">
+    <dataValidation type="list" allowBlank="1" promptTitle="角色填写" prompt="请选择“是”或“否”" sqref="F3:F5">
       <formula1>"管理员,成员"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C5">
       <formula1>"技术部,运营部,人事部"</formula1>
     </dataValidation>
   </dataValidations>
